--- a/docs/APIDocs/excel2img/examples/additional/inputs/wide-with-images.xlsx
+++ b/docs/APIDocs/excel2img/examples/additional/inputs/wide-with-images.xlsx
@@ -7,11 +7,11 @@
   </bookViews>
   <sheets>
     <sheet name="横長一覧と画像" r:id="rId3" sheetId="1"/>
-    <sheet name="52列・可読性不足" r:id="rId4" sheetId="2"/>
+    <sheet name="52列・横分割" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">横長一覧と画像!$A$1:$AA$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'52列・可読性不足'!$A$1:$AZ$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'52列・横分割'!$A$1:$AZ$29</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -248,18 +248,18 @@
   </si>
   <si>
     <t>・画像は表の右側のセル座標に固定しています。
-・図や文字を読むため、横方向は分割せず可読性の条件内で縮小します。
+・図や文字を読むため、可読性を保つ倍率まで縮小し、必要に応じて横方向に分割します。
 ・数値と画面は架空の内容です。業務データや実在システムの画面は含みません。</t>
   </si>
   <si>
     <t>このシートは約1,700ptの横幅で既定の描画条件に収まる想定です。
-次の52列シートは幅が大きすぎるためスキップされ、変換結果のreport.jsonに理由が記録される比較用です。</t>
-  </si>
-  <si>
-    <t>比較用 / 52列は横幅を縮小すると11ptの文字が読みにくくなる</t>
-  </si>
-  <si>
-    <t>このシートは既定設定で WIDTH_UNREADABLE としてスキップされる想定です。</t>
+次の52列シートは幅が大きいため複数ページに横分割され、report.jsonにページごとの範囲が記録される比較用です。</t>
+  </si>
+  <si>
+    <t>横分割の比較 / 52列を読める文字サイズのまま複数ページへ</t>
+  </si>
+  <si>
+    <t>文字の可読性を保てる倍率まで縮小し、それでも広い範囲は左から右へ分割して出力します。</t>
   </si>
   <si>
     <t>項目</t>
@@ -745,7 +745,7 @@
     <t>199</t>
   </si>
   <si>
-    <t>確認ポイント：無理に小さな画像にせず、この範囲をスキップして他の読めるシートは出力します。</t>
+    <t>確認ポイント：ページの左右を順につなぐと元の横長範囲になります。端の列、結合見出し、画像の位置も比較します。</t>
   </si>
 </sst>
 </file>
